--- a/data/trans_dic/IP16B02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16B02-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre (tasa de respuesta: 98,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,19; 77,0</t>
+          <t>30,62; 80,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67,51; 96,03</t>
+          <t>67,53; 96,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,19; 91,86</t>
+          <t>43,92; 92,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61,12; 100,0</t>
+          <t>68,58; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,98; 95,99</t>
+          <t>70,54; 95,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,76; 100,0</t>
+          <t>57,18; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,64; 86,52</t>
+          <t>53,62; 87,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>75,85; 94,15</t>
+          <t>75,94; 95,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55,43; 91,53</t>
+          <t>55,73; 91,47</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,94; 100,0</t>
+          <t>64,3; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,82; 86,5</t>
+          <t>58,47; 88,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,84; 96,9</t>
+          <t>71,99; 96,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72,65; 96,81</t>
+          <t>76,11; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,15; 100,0</t>
+          <t>78,0; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,96; 96,79</t>
+          <t>72,0; 96,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,01; 95,77</t>
+          <t>76,18; 95,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>70,42; 90,49</t>
+          <t>71,85; 90,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76,47; 94,68</t>
+          <t>77,05; 95,04</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76,09; 100,0</t>
+          <t>72,93; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,03; 93,38</t>
+          <t>64,04; 93,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,26; 94,65</t>
+          <t>57,76; 94,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64,97; 95,42</t>
+          <t>62,56; 95,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,27; 93,61</t>
+          <t>63,96; 93,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,07; 100,0</t>
+          <t>72,17; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,18; 95,32</t>
+          <t>73,94; 95,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,15; 91,33</t>
+          <t>70,53; 91,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73,1; 94,85</t>
+          <t>70,82; 93,42</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,88; 100,0</t>
+          <t>56,99; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,39; 93,18</t>
+          <t>65,15; 93,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,32; 96,45</t>
+          <t>71,96; 96,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73,01; 100,0</t>
+          <t>72,45; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,7; 96,66</t>
+          <t>67,18; 96,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,63; 100,0</t>
+          <t>71,16; 100,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,82; 96,97</t>
+          <t>72,81; 96,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>72,68; 92,43</t>
+          <t>73,59; 92,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,44; 97,56</t>
+          <t>77,6; 97,57</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>68,76; 88,59</t>
+          <t>67,27; 88,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72,45; 87,43</t>
+          <t>72,48; 87,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,84; 90,06</t>
+          <t>73,71; 90,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,33; 94,24</t>
+          <t>80,01; 94,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,6; 92,79</t>
+          <t>79,87; 93,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,35; 96,15</t>
+          <t>83,34; 95,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,8; 90,46</t>
+          <t>79,44; 90,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77,77; 88,87</t>
+          <t>79,11; 88,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>81,04; 91,57</t>
+          <t>80,82; 91,34</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos recetados por el médico para el dolor y/o para bajar la fiebre (tasa de respuesta: 98,35%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13545</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7974</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8008</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14881</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5982</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13331</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>28426</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>13955</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3034; 7938</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10499; 14931</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4918; 10336</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5940; 8662</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11995; 16324</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3793; 6634</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>9957; 16321</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>24719; 31143</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>9937; 16310</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>9271</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18586</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16661</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17337</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16981</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>16083</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26609</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>35567</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>32745</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6785; 10553</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14526; 21907</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>13676; 18372</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14696; 19310</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>14274; 18301</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>13007; 17492</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>22749; 28581</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>30998; 39173</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>28555; 35224</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8471</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14394</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10753</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13125</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16317</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13075</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>21596</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>30710</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>23828</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>6509; 8925</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11210; 16284</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7766; 12713</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9831; 15011</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12610; 18461</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10368; 14366</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>18220; 23456</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>26250; 33960</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>19695; 25979</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9556</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17157</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16224</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13677</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17061</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11896</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>23233</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>34217</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>28121</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6394; 11220</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13563; 19406</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13195; 17702</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10894; 15037</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>13134; 18875</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8977; 12614</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>19118; 25450</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>29707; 37414</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>24019; 30199</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>32622</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>63680</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>51613</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>52148</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>65240</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>47036</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84770</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>128920</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>98649</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>27316; 36076</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>57051; 68588</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>45684; 55848</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46984; 55411</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>59559; 69537</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>43068; 49505</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>78912; 89573</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>121270; 136264</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>91854; 103806</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B02-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16B02-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,62; 80,11</t>
+          <t>24,12; 76,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67,53; 96,04</t>
+          <t>67,43; 96,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,92; 92,31</t>
+          <t>46,05; 92,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68,58; 100,0</t>
+          <t>62,93; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,54; 95,99</t>
+          <t>70,26; 96,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,18; 100,0</t>
+          <t>52,51; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,62; 87,88</t>
+          <t>53,42; 86,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>75,94; 95,67</t>
+          <t>76,17; 95,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55,73; 91,47</t>
+          <t>55,59; 91,72</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,3; 100,0</t>
+          <t>63,43; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,47; 88,18</t>
+          <t>58,98; 87,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,99; 96,71</t>
+          <t>71,55; 96,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,11; 100,0</t>
+          <t>72,82; 96,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,0; 100,0</t>
+          <t>78,15; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,0; 96,83</t>
+          <t>70,31; 96,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,18; 95,71</t>
+          <t>77,62; 95,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>71,85; 90,8</t>
+          <t>71,42; 90,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>77,05; 95,04</t>
+          <t>77,44; 94,14</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,93; 100,0</t>
+          <t>78,34; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,04; 93,03</t>
+          <t>65,0; 92,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,76; 94,56</t>
+          <t>59,73; 94,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62,56; 95,51</t>
+          <t>65,8; 95,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,96; 93,64</t>
+          <t>66,01; 93,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,17; 100,0</t>
+          <t>72,36; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,94; 95,2</t>
+          <t>72,48; 95,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70,53; 91,25</t>
+          <t>70,18; 91,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,82; 93,42</t>
+          <t>71,86; 94,67</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,99; 100,0</t>
+          <t>56,77; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,15; 93,21</t>
+          <t>64,45; 93,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,96; 96,54</t>
+          <t>70,46; 96,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72,45; 100,0</t>
+          <t>72,15; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,18; 96,54</t>
+          <t>67,14; 96,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,16; 100,0</t>
+          <t>70,72; 100,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,81; 96,93</t>
+          <t>74,08; 97,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73,59; 92,68</t>
+          <t>72,38; 92,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,6; 97,57</t>
+          <t>77,62; 97,52</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>67,27; 88,84</t>
+          <t>68,48; 88,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72,48; 87,14</t>
+          <t>72,72; 87,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,71; 90,11</t>
+          <t>74,2; 89,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80,01; 94,36</t>
+          <t>82,08; 94,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,87; 93,25</t>
+          <t>79,63; 93,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,34; 95,79</t>
+          <t>82,2; 96,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,44; 90,18</t>
+          <t>78,57; 90,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,11; 88,9</t>
+          <t>78,87; 88,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80,82; 91,34</t>
+          <t>80,87; 91,38</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3034; 7938</t>
+          <t>2390; 7600</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10499; 14931</t>
+          <t>10484; 14932</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4918; 10336</t>
+          <t>5156; 10345</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5940; 8662</t>
+          <t>5451; 8662</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11995; 16324</t>
+          <t>11948; 16326</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3793; 6634</t>
+          <t>3483; 6634</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9957; 16321</t>
+          <t>9921; 16035</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24719; 31143</t>
+          <t>24795; 31156</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9937; 16310</t>
+          <t>9913; 16355</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6785; 10553</t>
+          <t>6694; 10553</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14526; 21907</t>
+          <t>14652; 21700</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13676; 18372</t>
+          <t>13593; 18411</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14696; 19310</t>
+          <t>14061; 18700</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14274; 18301</t>
+          <t>14302; 18301</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13007; 17492</t>
+          <t>12701; 17485</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22749; 28581</t>
+          <t>23178; 28585</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30998; 39173</t>
+          <t>30814; 39127</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28555; 35224</t>
+          <t>28701; 34889</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6509; 8925</t>
+          <t>6992; 8925</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11210; 16284</t>
+          <t>11377; 16262</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7766; 12713</t>
+          <t>8030; 12717</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9831; 15011</t>
+          <t>10342; 15043</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12610; 18461</t>
+          <t>13015; 18485</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10368; 14366</t>
+          <t>10395; 14366</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18220; 23456</t>
+          <t>17859; 23499</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26250; 33960</t>
+          <t>26121; 34050</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19695; 25979</t>
+          <t>19983; 26329</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6394; 11220</t>
+          <t>6369; 11220</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13563; 19406</t>
+          <t>13417; 19418</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13195; 17702</t>
+          <t>12919; 17685</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10894; 15037</t>
+          <t>10849; 15037</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13134; 18875</t>
+          <t>13127; 18904</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8977; 12614</t>
+          <t>8921; 12614</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19118; 25450</t>
+          <t>19451; 25552</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29707; 37414</t>
+          <t>29219; 37387</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24019; 30199</t>
+          <t>24025; 30184</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27316; 36076</t>
+          <t>27806; 36010</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>57051; 68588</t>
+          <t>57235; 68961</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45684; 55848</t>
+          <t>45988; 55696</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46984; 55411</t>
+          <t>48201; 55538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>59559; 69537</t>
+          <t>59379; 69492</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>43068; 49505</t>
+          <t>42480; 49702</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78912; 89573</t>
+          <t>78049; 89912</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>121270; 136264</t>
+          <t>120894; 135732</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>91854; 103806</t>
+          <t>91907; 103862</t>
         </is>
       </c>
     </row>
